--- a/outputs/545-35.xlsx
+++ b/outputs/545-35.xlsx
@@ -279,55 +279,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
